--- a/SeleniumTests/TestDataFolder/ReportTestDataNegative.xlsx
+++ b/SeleniumTests/TestDataFolder/ReportTestDataNegative.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\e-invoice\SeleniumTests\TestDataFolder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{055225C2-50F6-4787-BAE4-B3515FFAB4BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B792C867-249A-4F1A-B9B0-5368E86AAD28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="540" yWindow="1212" windowWidth="18312" windowHeight="10836" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ExportReportTestData" sheetId="1" r:id="rId1"/>
@@ -36,15 +36,9 @@
     <t>To Date</t>
   </si>
   <si>
-    <t>Doc Type</t>
-  </si>
-  <si>
     <t>All</t>
   </si>
   <si>
-    <t>Status</t>
-  </si>
-  <si>
     <t>Invoice, Credit Note</t>
   </si>
   <si>
@@ -67,6 +61,12 @@
   </si>
   <si>
     <t>Dec</t>
+  </si>
+  <si>
+    <t>Document Type</t>
+  </si>
+  <si>
+    <t>Document Status</t>
   </si>
 </sst>
 </file>
@@ -386,42 +386,53 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.21875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D1" t="s">
         <v>1</v>
       </c>
       <c r="E1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G1" t="s">
         <v>2</v>
       </c>
       <c r="H1" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="I1" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C2">
         <v>2025</v>
@@ -430,7 +441,7 @@
         <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F2">
         <v>2026</v>
@@ -439,10 +450,10 @@
         <v>1</v>
       </c>
       <c r="H2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
